--- a/data/trans_orig/P62A$jubilacion-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2007 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68651</t>
+          <t>68194</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81683</t>
+          <t>81904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>27052</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37478</t>
+          <t>38073</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99814</t>
+          <t>100151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>116504</t>
+          <t>117585</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>10365</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17471</t>
+          <t>18057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>22011</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4635</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5140</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67974</t>
+          <t>67988</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75160</t>
+          <t>75161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>21447</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81867</t>
+          <t>81529</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95439</t>
+          <t>95097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>8134</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6282</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>896</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9191</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>12093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>1132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93333</t>
+          <t>93484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107701</t>
+          <t>108349</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10234</t>
+          <t>10516</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18629</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107363</t>
+          <t>107949</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124972</t>
+          <t>124896</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>721</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>730</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>8316</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9465</t>
+          <t>8943</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22580</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,62 +2019,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>1756</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>1756</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>6091</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>320642</t>
+          <t>321427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>341723</t>
+          <t>341161</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67879</t>
+          <t>68191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87684</t>
+          <t>87359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397089</t>
+          <t>394307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424444</t>
+          <t>424261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,39%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11544</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27387</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29058</t>
+          <t>27943</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17176</t>
+          <t>18010</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36677</t>
+          <t>37029</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23208</t>
+          <t>22822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29220</t>
+          <t>29499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52078</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,46%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>7458</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3610</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14662</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>5727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>61913</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75519</t>
+          <t>75823</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44750</t>
+          <t>44797</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64686</t>
+          <t>64912</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111348</t>
+          <t>110652</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>137186</t>
+          <t>135899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>73,92%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24441</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42951</t>
+          <t>42062</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>23533</t>
+          <t>22916</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>43216</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19298</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>19919</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14713</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33772</t>
+          <t>33897</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>5792</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8471</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>851</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19125</t>
+          <t>19424</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39609</t>
+          <t>39428</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41323</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>208593</t>
+          <t>209624</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234258</t>
+          <t>234646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210138</t>
+          <t>208933</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237650</t>
+          <t>237437</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>19817</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>11939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>28828</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6142</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>637471</t>
+          <t>637882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>671802</t>
+          <t>672228</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>202158</t>
+          <t>201156</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>248046</t>
+          <t>247086</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>843049</t>
+          <t>847715</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>911975</t>
+          <t>916296</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,83%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>259080</t>
+          <t>262575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>307049</t>
+          <t>309304</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>257933</t>
+          <t>254451</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>318400</t>
+          <t>315671</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>56548</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>89910</t>
+          <t>88777</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>35221</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>60976</t>
+          <t>63012</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>100204</t>
+          <t>99617</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>141956</t>
+          <t>142612</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12510</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>17283</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39179</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23379</t>
+          <t>24370</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>47400</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51102</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64793</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21913</t>
+          <t>21728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>32154</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75966</t>
+          <t>76567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94113</t>
+          <t>94006</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -4272,12 +4272,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4287,12 +4287,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23326</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7288</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10355</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71539</t>
+          <t>70628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88077</t>
+          <t>88076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>85680</t>
+          <t>84865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108733</t>
+          <t>108182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,51%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12645</t>
+          <t>12056</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6377</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22569</t>
+          <t>23336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>15984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33072</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>130004</t>
+          <t>129076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>154847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31515</t>
+          <t>31485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46559</t>
+          <t>46312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>167136</t>
+          <t>167217</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>195870</t>
+          <t>195718</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,21%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10247</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7969</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21142</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>26497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>18095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39964</t>
+          <t>39293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>3226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24701</t>
+          <t>24794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48310</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,54%</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>22158</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>23930</t>
+          <t>24178</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>242982</t>
+          <t>244561</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>277053</t>
+          <t>278372</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>37933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61675</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>287261</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>331928</t>
+          <t>330719</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,03%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>28283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29575</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47770</t>
+          <t>50503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>78839</t>
+          <t>79813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22774</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>60919</t>
+          <t>62074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95234</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,52%</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>36236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24663</t>
+          <t>23948</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>44769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45818</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76189</t>
+          <t>76453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109332</t>
+          <t>109596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129347</t>
+          <t>129163</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108178</t>
+          <t>108802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>137729</t>
+          <t>138760</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>222210</t>
+          <t>224571</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261390</t>
+          <t>261531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,92%</t>
+          <t>68,96%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5595</t>
+          <t>5701</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48771</t>
+          <t>48808</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>48767</t>
+          <t>49821</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78472</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12592</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>22185</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>42897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39516</t>
+          <t>40232</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67034</t>
+          <t>67590</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>5864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>19381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11867</t>
+          <t>11426</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>29343</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42119</t>
+          <t>40821</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6407,12 +6407,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17140</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>204619</t>
+          <t>203614</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232051</t>
+          <t>230824</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>203498</t>
+          <t>202073</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>231932</t>
+          <t>232417</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7221</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21533</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>14324</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34395</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42105</t>
+          <t>42485</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>23914</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>46170</t>
+          <t>47245</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>635496</t>
+          <t>636914</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>690127</t>
+          <t>691230</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,12%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>241008</t>
+          <t>237849</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>292758</t>
+          <t>294880</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>890366</t>
+          <t>885287</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>971383</t>
+          <t>970631</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11342</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>296297</t>
+          <t>295144</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>350745</t>
+          <t>351803</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>296090</t>
+          <t>296262</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>363229</t>
+          <t>362176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118503</t>
+          <t>119005</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>166034</t>
+          <t>165409</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62068</t>
+          <t>61421</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>97117</t>
+          <t>96375</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>193488</t>
+          <t>193482</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>251188</t>
+          <t>255631</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43787</t>
+          <t>43562</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>74958</t>
+          <t>75107</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77770</t>
+          <t>77667</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>116024</t>
+          <t>116559</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>130879</t>
+          <t>129974</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>178760</t>
+          <t>180710</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2016 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80235</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93015</t>
+          <t>93195</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>123394</t>
+          <t>122509</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138924</t>
+          <t>138517</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -7698,97 +7698,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5715</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>1079</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>5830</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5505</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6018</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>894</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7831</t>
+          <t>7965</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>17847</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -7924,12 +7924,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61310</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73873</t>
+          <t>73799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16476</t>
+          <t>16344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28423</t>
+          <t>28465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81240</t>
+          <t>82558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100271</t>
+          <t>100435</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -8154,97 +8154,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2119</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>6562</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>18,03%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>2119</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>6534</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>7248</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>7635</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14333</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9461</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19549</t>
+          <t>19865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14550</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5793</t>
+          <t>5865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>20443</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140554</t>
+          <t>140115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158898</t>
+          <t>158955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28771</t>
+          <t>28515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42532</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>173624</t>
+          <t>174124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197156</t>
+          <t>196795</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12133</t>
+          <t>13497</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19890</t>
+          <t>19809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>933</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>8071</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8222</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23302</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -8836,12 +8836,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19755</t>
+          <t>20020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>12163</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9139</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>258634</t>
+          <t>261484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>291039</t>
+          <t>292130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68919</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>94851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337404</t>
+          <t>336267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377591</t>
+          <t>379476</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>28887</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26721</t>
+          <t>27342</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>51674</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>25989</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>40244</t>
+          <t>39186</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>72300</t>
+          <t>70540</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,39%</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9292,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>20943</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>42710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17617</t>
+          <t>17774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37374</t>
+          <t>37088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9362,12 +9362,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>42368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73179</t>
+          <t>71560</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>156728</t>
+          <t>155841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175530</t>
+          <t>175639</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109654</t>
+          <t>110977</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>139290</t>
+          <t>140277</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275361</t>
+          <t>271969</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>311093</t>
+          <t>308691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50798</t>
+          <t>50033</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>27450</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>50422</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31160</t>
+          <t>31059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28312</t>
+          <t>28610</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52692</t>
+          <t>52550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -9748,12 +9748,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>16501</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17375</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37041</t>
+          <t>37686</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25297</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48866</t>
+          <t>47497</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -9865,12 +9865,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9880,12 +9880,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12999</t>
+          <t>13573</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13771</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -9978,12 +9978,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9993,12 +9993,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>184170</t>
+          <t>183877</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210135</t>
+          <t>210595</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>182541</t>
+          <t>183881</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211011</t>
+          <t>209913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3228</t>
+          <t>3243</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2079</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6728</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20539</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>29272</t>
+          <t>28530</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>53937</t>
+          <t>52279</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30880</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>54617</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>727248</t>
+          <t>725623</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>773576</t>
+          <t>772081</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>291483</t>
+          <t>287914</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>347033</t>
+          <t>346245</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1030013</t>
+          <t>1027894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1112073</t>
+          <t>1110148</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,96%</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>235866</t>
+          <t>233771</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>290898</t>
+          <t>292338</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234664</t>
+          <t>234033</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>295124</t>
+          <t>298690</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>70784</t>
+          <t>71270</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>108104</t>
+          <t>107766</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>41136</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>70450</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>117631</t>
+          <t>118724</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>167333</t>
+          <t>165274</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -10660,12 +10660,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>44428</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>74836</t>
+          <t>76052</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>86734</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>127302</t>
+          <t>129242</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>144181</t>
+          <t>142751</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>192774</t>
+          <t>191506</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023</t>
+          <t>Población según el tipo de pensión que percibe (multirrespuesta) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54527</t>
+          <t>53933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>71381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,12 +11026,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11046,12 +11046,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35985</t>
+          <t>35465</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47867</t>
+          <t>47976</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11061,12 +11061,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11081,12 +11081,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94944</t>
+          <t>94181</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114888</t>
+          <t>114714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11096,12 +11096,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1564</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>9098</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1799</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8288</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1642</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23248</t>
+          <t>22741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38269</t>
+          <t>38409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11365,12 +11365,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20092</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>35060</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53981</t>
+          <t>54397</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -11467,12 +11467,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47215</t>
+          <t>47702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65856</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11482,12 +11482,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11502,12 +11502,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24688</t>
+          <t>23801</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35919</t>
+          <t>35559</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11517,12 +11517,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>75989</t>
+          <t>76673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97623</t>
+          <t>97841</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5839</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14122</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16113</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>31679</t>
+          <t>32212</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,16%</t>
         </is>
       </c>
     </row>
@@ -11698,7 +11698,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13061</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27303</t>
+          <t>27425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>43803</t>
+          <t>44185</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10519</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19979</t>
+          <t>20251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41098</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59268</t>
+          <t>59859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,6%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50354</t>
+          <t>50583</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70486</t>
+          <t>70093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11938,12 +11938,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17353</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27742</t>
+          <t>27561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71657</t>
+          <t>71526</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93268</t>
+          <t>93827</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,34%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21350</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38848</t>
+          <t>39005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8528</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>25234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>42472</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,24%</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4133</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17922</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9569</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19934</t>
+          <t>20227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32979</t>
+          <t>32700</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50631</t>
+          <t>51110</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>38,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>43166</t>
+          <t>42819</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62622</t>
+          <t>62780</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -12379,12 +12379,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147034</t>
+          <t>147247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175126</t>
+          <t>175749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12394,12 +12394,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>136687</t>
+          <t>135734</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>311237</t>
+          <t>310270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>314009</t>
+          <t>312344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>549481</t>
+          <t>548082</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,47%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36756</t>
+          <t>36328</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>61191</t>
+          <t>59058</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46666</t>
+          <t>46252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>21752</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99668</t>
+          <t>100523</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10842</t>
+          <t>10974</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>66944</t>
+          <t>68107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47543</t>
+          <t>46949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68404</t>
+          <t>68932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95023</t>
+          <t>95666</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>7647</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90466</t>
+          <t>90041</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44651</t>
+          <t>43801</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174084</t>
+          <t>176478</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57632</t>
+          <t>56654</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78455</t>
+          <t>78500</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>55871</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>73973</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12890,7 +12890,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>119647</t>
+          <t>118123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>147543</t>
+          <t>146731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15836</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31821</t>
+          <t>31791</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14744</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34056</t>
+          <t>34460</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>53682</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,12 +13033,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>542</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71126</t>
+          <t>71800</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91111</t>
+          <t>91993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73315</t>
+          <t>74124</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96195</t>
+          <t>96403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37680</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>57248</t>
+          <t>58830</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45822</t>
+          <t>45201</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64389</t>
+          <t>64876</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89070</t>
+          <t>89105</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>116339</t>
+          <t>115900</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16008</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,12 +13341,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13361,12 +13361,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13376,12 +13376,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7089</t>
+          <t>7351</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>8684</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4392</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14383</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13532,12 +13532,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>150431</t>
+          <t>149730</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167677</t>
+          <t>167157</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,12 +13567,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>148566</t>
+          <t>148574</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>167228</t>
+          <t>168253</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -13630,12 +13630,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>3180</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13645,12 +13645,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13665,12 +13665,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16011</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30395</t>
+          <t>30150</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13700,12 +13700,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>384935</t>
+          <t>383638</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>432983</t>
+          <t>432540</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>280137</t>
+          <t>278969</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>661775</t>
+          <t>667243</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>708049</t>
+          <t>708012</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1132076</t>
+          <t>1172297</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>68,37%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109315</t>
+          <t>109518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>145811</t>
+          <t>147924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79405</t>
+          <t>79793</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>121671</t>
+          <t>117463</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>222827</t>
+          <t>221125</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,9%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19225</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>153400</t>
+          <t>149012</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>377409</t>
+          <t>377029</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>202960</t>
+          <t>196518</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>347238</t>
+          <t>347774</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -14086,12 +14086,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>220725</t>
+          <t>221608</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>264479</t>
+          <t>265026</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14101,12 +14101,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14121,12 +14121,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>79732</t>
+          <t>78643</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>199283</t>
+          <t>200472</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14136,12 +14136,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14156,12 +14156,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>258021</t>
+          <t>242979</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>455907</t>
+          <t>454750</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14171,12 +14171,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,52%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P62A$jubilacion-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P62A$jubilacion-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>68194</t>
+          <t>69367</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>81662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27052</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>37570</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100151</t>
+          <t>100152</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>117585</t>
+          <t>117037</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1758</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10365</t>
+          <t>10618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1752</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>16998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67988</t>
+          <t>68010</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75161</t>
+          <t>75171</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10810</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21451</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>81529</t>
+          <t>80986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>95097</t>
+          <t>95321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,97%</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10098</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93484</t>
+          <t>92875</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>108349</t>
+          <t>107855</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10335</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107949</t>
+          <t>107990</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124896</t>
+          <t>124355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8943</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23683</t>
+          <t>23690</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>7125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>26476</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -1989,7 +1989,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>321427</t>
+          <t>321124</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>341161</t>
+          <t>341543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68191</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87359</t>
+          <t>85901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>394307</t>
+          <t>394685</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>424261</t>
+          <t>423222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,17%</t>
         </is>
       </c>
     </row>
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27038</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11253</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27943</t>
+          <t>28725</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18010</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37029</t>
+          <t>36850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22822</t>
+          <t>23443</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29499</t>
+          <t>29720</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>54391</t>
+          <t>52663</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>867</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>8765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3709</t>
+          <t>3558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14662</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61913</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>75823</t>
+          <t>75652</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44797</t>
+          <t>45033</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>64912</t>
+          <t>65892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110652</t>
+          <t>110568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135899</t>
+          <t>135827</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,88%</t>
         </is>
       </c>
     </row>
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42062</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43216</t>
+          <t>43777</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6067</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6071</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19919</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15344</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>33329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5792</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8471</t>
+          <t>8439</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>18285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39428</t>
+          <t>38878</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20319</t>
+          <t>20486</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>40759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4162</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>209624</t>
+          <t>208494</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>234646</t>
+          <t>234421</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>208933</t>
+          <t>209201</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237437</t>
+          <t>237381</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9513</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19817</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>19821</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6142</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>20561</t>
+          <t>19687</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>637882</t>
+          <t>636822</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>672228</t>
+          <t>671534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>201156</t>
+          <t>202254</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>247086</t>
+          <t>249874</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>847715</t>
+          <t>846314</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>916296</t>
+          <t>914237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>262575</t>
+          <t>261261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>309755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>254451</t>
+          <t>256493</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>315671</t>
+          <t>316851</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>56548</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>88777</t>
+          <t>89692</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63012</t>
+          <t>60881</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>99617</t>
+          <t>99676</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142612</t>
+          <t>141076</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12922</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17283</t>
+          <t>18706</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39179</t>
+          <t>40171</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24370</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>47400</t>
+          <t>47146</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4159,12 +4159,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51422</t>
+          <t>50982</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>64108</t>
+          <t>63928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21728</t>
+          <t>22135</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32154</t>
+          <t>32295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4209,12 +4209,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>76567</t>
+          <t>76760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>94006</t>
+          <t>94121</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -4307,12 +4307,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1865</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8093</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24075</t>
+          <t>22935</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>6428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -4615,12 +4615,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70628</t>
+          <t>71138</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88076</t>
+          <t>88480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>24221</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84865</t>
+          <t>86206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108182</t>
+          <t>109376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4700,12 +4700,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -4763,12 +4763,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1979</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11623</t>
+          <t>11425</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>22306</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2894</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15984</t>
+          <t>16175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>31597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,81%</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3656</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>15578</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19328</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5071,12 +5071,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>129076</t>
+          <t>130169</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154847</t>
+          <t>154088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31485</t>
+          <t>31535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46312</t>
+          <t>45920</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>167217</t>
+          <t>166800</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>195718</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5156,12 +5156,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>8035</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9827</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26497</t>
+          <t>26592</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18095</t>
+          <t>18722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>14989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24770</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47675</t>
+          <t>48049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,69%</t>
         </is>
       </c>
     </row>
@@ -5410,12 +5410,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6584</t>
+          <t>6567</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22158</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5425,12 +5425,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>7602</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>24178</t>
+          <t>24616</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>244561</t>
+          <t>241685</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>278372</t>
+          <t>277493</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>39333</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>61411</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>288686</t>
+          <t>288938</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330719</t>
+          <t>330840</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,05%</t>
         </is>
       </c>
     </row>
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28283</t>
+          <t>27682</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10677</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29036</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50503</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>79813</t>
+          <t>79367</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7409</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62074</t>
+          <t>60879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95569</t>
+          <t>95837</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -5866,12 +5866,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15105</t>
+          <t>16663</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36236</t>
+          <t>38672</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23948</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>44769</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46356</t>
+          <t>45673</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76453</t>
+          <t>76055</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>109596</t>
+          <t>108807</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>129163</t>
+          <t>129257</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108802</t>
+          <t>108521</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>138760</t>
+          <t>140063</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224571</t>
+          <t>221195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261531</t>
+          <t>261650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48808</t>
+          <t>48809</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>76169</t>
+          <t>75673</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>49821</t>
+          <t>48605</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>78368</t>
+          <t>78754</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>12698</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29616</t>
+          <t>30175</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>21565</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>43234</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67590</t>
+          <t>67047</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5864</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19381</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6337,12 +6337,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11426</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29343</t>
+          <t>28451</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6372,12 +6372,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>21268</t>
+          <t>20678</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40821</t>
+          <t>41905</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6407,19 +6407,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6459,7 +6459,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3233</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>16695</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>203614</t>
+          <t>202970</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>230824</t>
+          <t>230270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>202073</t>
+          <t>201094</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>232417</t>
+          <t>231356</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5456</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13991</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21924</t>
+          <t>23006</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>14324</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>33966</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,9%</t>
         </is>
       </c>
     </row>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>946</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>8098</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6793,12 +6793,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>21094</t>
+          <t>20768</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>42485</t>
+          <t>42822</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6828,12 +6828,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>24391</t>
+          <t>24627</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>47245</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>636914</t>
+          <t>637961</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>691230</t>
+          <t>690705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>237849</t>
+          <t>239898</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294880</t>
+          <t>292368</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>885287</t>
+          <t>888941</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>970631</t>
+          <t>971648</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,19%</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12303</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>295144</t>
+          <t>297225</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>351803</t>
+          <t>350528</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>296262</t>
+          <t>296464</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>362176</t>
+          <t>359396</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119005</t>
+          <t>119438</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165409</t>
+          <t>167404</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>61421</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96375</t>
+          <t>97020</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>193482</t>
+          <t>195386</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>255631</t>
+          <t>253910</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -7234,12 +7234,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>43553</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>75107</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>77667</t>
+          <t>78302</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>116559</t>
+          <t>117625</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>130806</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>180710</t>
+          <t>181534</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7319,12 +7319,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -7585,12 +7585,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>79933</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93195</t>
+          <t>93024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7600,12 +7600,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7620,12 +7620,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>47531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122509</t>
+          <t>124100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138517</t>
+          <t>138258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7670,12 +7670,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7753,7 +7753,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5666</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7811,47 +7811,47 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14463</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>2970</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>14221</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>7,31%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2970</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>895</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7413</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>862</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>7016</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7974,12 +7974,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12281</t>
+          <t>11963</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -8041,12 +8041,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>61617</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73799</t>
+          <t>73669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28553</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>82558</t>
+          <t>81801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>100435</t>
+          <t>100052</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8126,12 +8126,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8229,7 +8229,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14534</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,12 +8302,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -8380,12 +8380,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>976</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8353</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8415,12 +8415,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>14640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8430,12 +8430,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5865</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20443</t>
+          <t>19300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8465,12 +8465,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -8497,12 +8497,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140115</t>
+          <t>140625</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>158955</t>
+          <t>158734</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,12 +8532,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>28515</t>
+          <t>28563</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>42454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8547,12 +8547,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8567,12 +8567,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174124</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>196795</t>
+          <t>198681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8582,12 +8582,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>89,15%</t>
         </is>
       </c>
     </row>
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>13015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>12281</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>19790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8166</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -8836,12 +8836,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20119</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8851,12 +8851,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8871,12 +8871,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12241</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8886,12 +8886,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8906,12 +8906,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>9314</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>26690</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>261484</t>
+          <t>258099</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>292130</t>
+          <t>290371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>69983</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94851</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>336267</t>
+          <t>336781</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>379476</t>
+          <t>378510</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,59%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,2%</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>28887</t>
+          <t>29710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31306</t>
+          <t>32870</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27342</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51674</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25989</t>
+          <t>26000</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39186</t>
+          <t>39394</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70540</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -9292,12 +9292,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20943</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42710</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9307,12 +9307,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9327,12 +9327,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17774</t>
+          <t>17386</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37088</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9342,12 +9342,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9362,12 +9362,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>42368</t>
+          <t>42705</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>73202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155841</t>
+          <t>157041</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>175938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110977</t>
+          <t>109831</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>140277</t>
+          <t>140056</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>271969</t>
+          <t>272508</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>308691</t>
+          <t>309684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>27337</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>50033</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27450</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>51732</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10535</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>27118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>32198</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28610</t>
+          <t>28787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>52550</t>
+          <t>53232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -9748,12 +9748,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16501</t>
+          <t>16827</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9763,12 +9763,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9783,12 +9783,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17680</t>
+          <t>17309</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>25128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>47497</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9833,19 +9833,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2436</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13573</t>
+          <t>13795</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2549</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>183877</t>
+          <t>183430</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210595</t>
+          <t>210454</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>183881</t>
+          <t>182565</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>209913</t>
+          <t>210379</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,82%</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3243</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10106,7 +10106,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6469</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>21569</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10224,7 +10224,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28530</t>
+          <t>29732</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>54057</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10254,12 +10254,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>30263</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>55422</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>725623</t>
+          <t>725719</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>772081</t>
+          <t>772036</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>287914</t>
+          <t>290663</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>346245</t>
+          <t>346905</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1027894</t>
+          <t>1028300</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1110148</t>
+          <t>1110779</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>68,0%</t>
         </is>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5228</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>233771</t>
+          <t>237298</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>292338</t>
+          <t>293879</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>234033</t>
+          <t>233461</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>298690</t>
+          <t>298812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>71270</t>
+          <t>71578</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>107766</t>
+          <t>109833</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41136</t>
+          <t>40509</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70450</t>
+          <t>72175</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>118724</t>
+          <t>120854</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>165274</t>
+          <t>167753</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -10660,12 +10660,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>46121</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>76052</t>
+          <t>76128</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10675,12 +10675,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>86734</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>128981</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10710,12 +10710,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10730,12 +10730,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>142751</t>
+          <t>142932</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>191506</t>
+          <t>192327</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10745,12 +10745,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>63095</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>53933</t>
+          <t>61501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71381</t>
+          <t>79441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,32 +11041,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42044</t>
+          <t>48221</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35465</t>
+          <t>41612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47976</t>
+          <t>54546</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>105140</t>
+          <t>119203</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94181</t>
+          <t>107219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114714</t>
+          <t>130029</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,6%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17877</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1654</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>8599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14397</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -11345,32 +11345,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29804</t>
+          <t>34038</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>25723</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>43179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9782</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>21051</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>49469</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35060</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -11462,32 +11462,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47702</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>64951</t>
+          <t>71810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,26%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,32 +11497,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35559</t>
+          <t>40681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>86569</t>
+          <t>97021</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76673</t>
+          <t>85884</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97841</t>
+          <t>109496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>59,08%</t>
         </is>
       </c>
     </row>
@@ -11575,32 +11575,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>14333</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8577</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21600</t>
+          <t>22679</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9606</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5839</t>
+          <t>6570</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>16331</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>23698</t>
+          <t>25066</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32212</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -11698,12 +11698,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3433</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>11421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>8398</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>38407</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>30646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44185</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11836,32 +11836,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>16457</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9943</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>22776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>44831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>59859</t>
+          <t>64788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,95%</t>
         </is>
       </c>
     </row>
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>70093</t>
+          <t>75210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22167</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>19127</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27561</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,32 +11988,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>82403</t>
+          <t>89614</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>71526</t>
+          <t>77666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>93827</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>28811</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>22519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39005</t>
+          <t>40307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4914</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>9020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>33567</t>
+          <t>35688</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25234</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>46794</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -12154,12 +12154,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -12169,7 +12169,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>20293</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>15689</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9665</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20227</t>
+          <t>22364</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -12257,32 +12257,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>46313</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32700</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51110</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12292,32 +12292,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11712</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>8464</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12327,32 +12327,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>52570</t>
+          <t>59119</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42819</t>
+          <t>48354</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>62780</t>
+          <t>69885</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>161317</t>
+          <t>175798</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>147247</t>
+          <t>160757</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175749</t>
+          <t>192455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>54,66%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>260024</t>
+          <t>59412</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135734</t>
+          <t>50873</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>310270</t>
+          <t>68359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>421342</t>
+          <t>235211</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>312344</t>
+          <t>218088</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>548082</t>
+          <t>255548</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>55,65%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>47419</t>
+          <t>49312</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36328</t>
+          <t>38053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59058</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15900</t>
+          <t>16553</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>63318</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21752</t>
+          <t>53520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>100523</t>
+          <t>81416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10974</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>24853</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68107</t>
+          <t>33387</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>28799</t>
+          <t>30336</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10814</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46949</t>
+          <t>40434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12713,32 +12713,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>90951</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>68932</t>
+          <t>77587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>95666</t>
+          <t>107085</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12748,32 +12748,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31926</t>
+          <t>36844</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>29749</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>90041</t>
+          <t>46260</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12783,32 +12783,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>113113</t>
+          <t>127795</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43801</t>
+          <t>110513</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>176478</t>
+          <t>144224</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>31,41%</t>
         </is>
       </c>
     </row>
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>67774</t>
+          <t>72249</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56654</t>
+          <t>60595</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78500</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,32 +12865,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>65012</t>
+          <t>70784</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>55871</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>73973</t>
+          <t>81811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12900,32 +12900,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>132786</t>
+          <t>143033</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>118123</t>
+          <t>128512</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146731</t>
+          <t>156831</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,88%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>23111</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15836</t>
+          <t>15799</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31791</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15664</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>29643</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>43238</t>
+          <t>45413</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34460</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>53682</t>
+          <t>56104</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,32 +13091,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81320</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>71800</t>
+          <t>76607</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91993</t>
+          <t>99586</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>84508</t>
+          <t>90859</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74124</t>
+          <t>78597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96403</t>
+          <t>104071</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -13169,32 +13169,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>52251</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>37327</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>58830</t>
+          <t>64740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13204,32 +13204,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>54773</t>
+          <t>61733</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45201</t>
+          <t>51911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>64876</t>
+          <t>72809</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13239,39 +13239,39 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>102002</t>
+          <t>113984</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>89105</t>
+          <t>98973</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>115900</t>
+          <t>129587</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10017</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>18925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>10538</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6243</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -13399,32 +13399,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7351</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2106</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8684</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>8213</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4392</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>13935</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>171998</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149730</t>
+          <t>161922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>167157</t>
+          <t>180069</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>159411</t>
+          <t>171998</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>148574</t>
+          <t>161366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>168253</t>
+          <t>181931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -13625,32 +13625,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3180</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13660,32 +13660,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>22098</t>
+          <t>22774</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>30150</t>
+          <t>31113</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13695,32 +13695,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>29269</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>20911</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>37781</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>409655</t>
+          <t>447057</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>383638</t>
+          <t>420963</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>432540</t>
+          <t>472513</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>429121</t>
+          <t>249365</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>278969</t>
+          <t>230685</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>667243</t>
+          <t>270787</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>838777</t>
+          <t>696422</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>708012</t>
+          <t>661153</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1172297</t>
+          <t>730775</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>44,31%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>127603</t>
+          <t>132875</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>109518</t>
+          <t>115936</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>147924</t>
+          <t>154705</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>58878</t>
+          <t>63757</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29316</t>
+          <t>52403</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>79793</t>
+          <t>76033</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>186481</t>
+          <t>196633</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>117463</t>
+          <t>174574</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>221125</t>
+          <t>221484</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18626</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>287339</t>
+          <t>310118</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>149012</t>
+          <t>289329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>377029</t>
+          <t>330124</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>298487</t>
+          <t>321759</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>196518</t>
+          <t>297684</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>347774</t>
+          <t>347625</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -14081,32 +14081,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>241178</t>
+          <t>268454</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>221608</t>
+          <t>245914</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>265026</t>
+          <t>295727</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14116,32 +14116,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>149828</t>
+          <t>166046</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>148693</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>200472</t>
+          <t>184006</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14151,32 +14151,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>391007</t>
+          <t>434500</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>242979</t>
+          <t>404697</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>454750</t>
+          <t>464903</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
